--- a/SGC-CKN/Excel/b73bc3da-6751-49cb-a747-71fca4f82417_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-01_D800_18-03-2026.xlsx
+++ b/SGC-CKN/Excel/b73bc3da-6751-49cb-a747-71fca4f82417_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-01_D800_18-03-2026.xlsx
@@ -17,7 +17,7 @@
     <t>Dự án</t>
   </si>
   <si>
-    <t>Dự án số 1 khu đô thị trung tâm thành phố Thanh Hóa (Vinhomes Star City)</t>
+    <t>Star City Thanh Hóa</t>
   </si>
   <si>
     <t>Hạng mục</t>
@@ -38,10 +38,10 @@
     <t>P11-01</t>
   </si>
   <si>
-    <t>Biên bản số</t>
-  </si>
-  <si>
-    <t/>
+    <t>Tên Máy khoan</t>
+  </si>
+  <si>
+    <t>SGCT-KCN0003</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Sét pha, xám nâu, TT dẻo mềm</t>
+    <t>Sét pha, xám xanh, xám đen, xám nâu, xám ghi, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">01:20
@@ -106,10 +106,13 @@
 18/03/2026</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">02:00
@@ -119,7 +122,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét- đôi chỗ kép cát pha, lẫn dăm sạn TT dẻo mềm</t>
+    <t>Sét, đôi chỗ kẹp cát pha, lẫn dăm sạn TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">03:00
@@ -139,9 +142,6 @@
     <t>5</t>
   </si>
   <si>
-    <t>Sét pha, xám xanh, xám ghi, TT dẻo mềm lẫn hữu cơ, kẹp cát</t>
-  </si>
-  <si>
     <t xml:space="preserve">04:00
 18/03/2026</t>
   </si>
@@ -149,7 +149,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát pha, xám vàng, xám ghi TT dẻo</t>
+    <t>Cát pha xám ghi, xám nâu, xám vàng TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">05:00
@@ -159,7 +159,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ là hạt cát nhỏ bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, xám nâu TT chặt</t>
   </si>
   <si>
     <t xml:space="preserve">05:44
@@ -169,7 +169,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">07:50
@@ -1160,24 +1160,24 @@
         <v>3.6</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F12" s="9">
         <v>-2.9</v>
@@ -1195,24 +1195,24 @@
         <v>31.2</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13" s="13">
         <v>-13.3</v>
@@ -1230,24 +1230,24 @@
         <v>5</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F14" s="16">
         <v>-18.3</v>
@@ -1265,21 +1265,21 @@
         <v>22.4</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E15" s="21" t="s">
         <v>41</v>
@@ -1300,7 +1300,7 @@
         <v>12.2</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1335,7 +1335,7 @@
         <v>2.8</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1370,7 +1370,7 @@
         <v>8.59</v>
       </c>
       <c r="K17" s="26" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1580,7 +1580,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1609,7 +1609,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="13">
         <v>1</v>
@@ -1638,7 +1638,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -1667,7 +1667,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -1780,10 +1780,10 @@
         <v>61</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D10" s="33">
         <v>8</v>
